--- a/data/trans_camb/IQ2605_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IQ2605_R2-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11,58</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,16</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12,14</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>9,78</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-0,55</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>17,91</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11,58</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,16</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,26</t>
+          <t>18,46</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12,9</t>
+          <t>15,3</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 18,39</t>
+          <t>4,48; 19,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 8,19</t>
+          <t>-6,78; 10,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,53; 26,98</t>
+          <t>-8,08; 22,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,57; 19,19</t>
+          <t>1,33; 18,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 11,1</t>
+          <t>-9,99; 9,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,22; 21,17</t>
+          <t>4,99; 28,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,54; 16,64</t>
+          <t>4,61; 16,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 7,31</t>
+          <t>-5,04; 7,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 21,51</t>
+          <t>4,14; 22,62</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>14,74%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>15,45%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>12,92%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-0,73%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>23,66%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>14,74%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>19,8%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 26,51</t>
+          <t>5,49; 27,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 11,92</t>
+          <t>-8,1; 14,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,78; 38,27</t>
+          <t>-8,91; 29,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,34; 26,6</t>
+          <t>2,06; 26,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 15,5</t>
+          <t>-12,11; 13,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-21,39; 27,23</t>
+          <t>7,48; 40,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,7; 23,05</t>
+          <t>5,69; 22,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 10,25</t>
+          <t>-6,28; 10,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 29,11</t>
+          <t>5,65; 31,02</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>24,95</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>31,35</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>34,17</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>17,25</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>24,9</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>25,78</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>24,95</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>31,35</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,4</t>
+          <t>25,85</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>30,24</t>
+          <t>30,14</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,91; 23,55</t>
+          <t>17,6; 31,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,21; 30,54</t>
+          <t>25,49; 38,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,5; 34,62</t>
+          <t>22,17; 43,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,29; 31,95</t>
+          <t>10,28; 24,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,09; 37,45</t>
+          <t>18,88; 31,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,82; 42,87</t>
+          <t>16,14; 35,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,33; 26,27</t>
+          <t>16,47; 25,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>23,39; 32,7</t>
+          <t>23,9; 32,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,71; 36,27</t>
+          <t>21,9; 36,18</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>47,16%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>59,25%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>64,57%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>29,08%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>41,98%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>43,47%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>47,16%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>59,25%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>53,71%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,05; 42,69</t>
+          <t>30,62; 64,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,04; 55,21</t>
+          <t>44,78; 79,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,45; 61,86</t>
+          <t>41,61; 88,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32,43; 67,21</t>
+          <t>16,63; 44,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>43,74; 76,25</t>
+          <t>30,07; 56,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,02; 87,93</t>
+          <t>26,46; 63,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,02; 49,28</t>
+          <t>28,07; 48,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>40,25; 61,64</t>
+          <t>40,56; 61,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>37,55; 66,98</t>
+          <t>37,9; 66,99</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>13,18</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>27,8</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>20,09</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>27,13</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>28,05</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>24,6</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>13,18</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>27,8</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,41</t>
+          <t>24,22</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21,76</t>
+          <t>22,0</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,98; 35,42</t>
+          <t>4,59; 23,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,47; 35,95</t>
+          <t>19,75; 36,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,1; 39,56</t>
+          <t>6,04; 33,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,75; 21,72</t>
+          <t>18,09; 35,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,35; 36,42</t>
+          <t>18,36; 36,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,85; 30,68</t>
+          <t>8,66; 37,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,36; 26,2</t>
+          <t>13,52; 26,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,6; 34,34</t>
+          <t>21,84; 34,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,15; 31,53</t>
+          <t>12,1; 31,58</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>26,14%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>55,16%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>39,86%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>57,52%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>59,47%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>52,17%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>26,14%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>55,16%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>45,02%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33,94; 87,01</t>
+          <t>8,66; 51,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32,88; 88,8</t>
+          <t>35,3; 83,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,98; 91,09</t>
+          <t>11,56; 73,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,78; 47,02</t>
+          <t>34,14; 87,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>34,52; 84,3</t>
+          <t>34,08; 88,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,19; 66,78</t>
+          <t>17,97; 88,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,82; 58,42</t>
+          <t>25,68; 59,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>41,0; 76,29</t>
+          <t>41,67; 77,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21,73; 67,18</t>
+          <t>22,48; 68,46</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>22,56</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>30,47</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>31,52</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>18,86</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>26,18</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>17,06</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>22,56</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>30,47</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,65</t>
+          <t>17,39</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>25,55</t>
+          <t>25,34</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,37; 27,4</t>
+          <t>14,02; 30,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,35; 34,1</t>
+          <t>22,57; 37,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,98; 29,1</t>
+          <t>18,93; 41,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,64; 30,99</t>
+          <t>9,42; 26,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,94; 38,97</t>
+          <t>17,39; 34,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,75; 42,21</t>
+          <t>3,55; 28,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,05; 26,4</t>
+          <t>14,79; 26,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>22,73; 33,84</t>
+          <t>22,51; 33,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16,57; 33,54</t>
+          <t>16,36; 33,83</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>54,82%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>74,03%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>76,58%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>45,66%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>63,38%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>41,29%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>54,82%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>74,03%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>61,45%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>23,8; 75,28</t>
+          <t>30,3; 80,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>37,91; 93,88</t>
+          <t>49,83; 102,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,21; 77,48</t>
+          <t>43,38; 109,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32,02; 85,91</t>
+          <t>20,69; 73,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>50,45; 107,02</t>
+          <t>36,83; 92,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>43,19; 113,74</t>
+          <t>8,76; 74,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,65; 68,28</t>
+          <t>33,29; 69,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>50,56; 88,38</t>
+          <t>50,39; 89,4</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>38,39; 86,02</t>
+          <t>37,1; 85,93</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>20,39</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>26,33</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>23,5</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>19,66</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>22,07</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>17,97</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>20,39</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>26,33</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,52</t>
+          <t>17,28</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>21,08</t>
+          <t>20,72</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15,42; 23,83</t>
+          <t>16,46; 23,92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>18,16; 26,21</t>
+          <t>22,41; 29,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,12; 24,55</t>
+          <t>16,5; 29,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15,86; 24,16</t>
+          <t>14,95; 23,58</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21,8; 30,24</t>
+          <t>17,88; 25,94</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,6; 29,91</t>
+          <t>10,04; 24,29</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,24; 23,07</t>
+          <t>17,28; 23,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>21,38; 27,05</t>
+          <t>21,7; 27,12</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>16,78; 25,71</t>
+          <t>15,52; 25,44</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>38,58%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>49,83%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>44,47%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>36,43%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>40,9%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>33,3%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>38,58%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>49,83%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>38,82%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>27,33; 46,42</t>
+          <t>29,64; 47,61</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>31,96; 51,59</t>
+          <t>40,71; 59,33</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20,07; 46,64</t>
+          <t>30,52; 57,89</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>28,42; 48,02</t>
+          <t>26,63; 46,15</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>39,74; 59,9</t>
+          <t>31,9; 50,8</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,1; 58,53</t>
+          <t>18,31; 46,55</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,49; 44,79</t>
+          <t>31,36; 44,54</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>38,5; 52,0</t>
+          <t>39,46; 52,87</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>30,61; 49,25</t>
+          <t>28,4; 49,1</t>
         </is>
       </c>
     </row>
